--- a/icons-study/03-mapping-sysml1-vers-sysml2.xlsx
+++ b/icons-study/03-mapping-sysml1-vers-sysml2.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="90" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,12 +483,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>chemin_source</t>
+          <t>chemin_icone_source</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>chemin_destination</t>
+          <t>chemin_icone_sysml2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>avancement</t>
         </is>
       </c>
     </row>
@@ -524,17 +530,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Block v1 se scinde en couple Definition/Usage</t>
+          <t>Block v1 se scinde en couple Definition/Usage - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\block.png</t>
+          <t>icons-study/07-icones-sources/sysml1/block.png</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/block.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.partdefinition.svg / icons-study/08-icones-sysml2/sysml.partusage.svg</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -567,17 +578,22 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Definition correspondante = PartDefinition, couverte par la ligne block</t>
+          <t>Definition correspondante = PartDefinition, couverte par la ligne block - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\part.png</t>
+          <t>icons-study/07-icones-sources/sysml1/part.png</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/part.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.partusage.svg</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -612,15 +628,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\constraintblock.png</t>
+          <t>icons-study/07-icones-sources/sysml1/constraintblock.png</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/constraintblock.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.constraintdefinition.svg / icons-study/08-icones-sysml2/sysml.constraintusage.svg</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -653,17 +678,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>usage en tant que feature typee - Definition couverte par la ligne constraintblock - visuel coherent (symbole accolades {}), confirme comme la vraie base pour ConstraintUsage (verifie visuellement le 2026-09-24, a distinguer de constraint.png qui n'est pas pertinent)</t>
+          <t>usage en tant que feature typee - Definition couverte par la ligne constraintblock - visuel coherent (symbole accolades {}), confirme comme la vraie base pour ConstraintUsage (verifie visuellement le 2026-09-24, a distinguer de constraint.png qui n'est pas pertinent) - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\constraintproperty.png</t>
+          <t>icons-study/07-icones-sources/sysml1/constraintproperty.png</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/constraintproperty.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.constraintusage.svg</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -696,17 +726,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ValueType v1 -&gt; AttributeDefinition en v2 - icone contient les lettres VT gravees en dur dans les pixels, valable uniquement pour la Definition (verifie visuellement le 2026-09-24) - AttributeUsage retiree de cette ligne, couverte separement</t>
+          <t>ValueType v1 -&gt; AttributeDefinition en v2 - icone contient les lettres VT gravees en dur dans les pixels, valable uniquement pour la Definition (verifie visuellement le 2026-09-24) - AttributeUsage retiree de cette ligne, couverte separement - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\valuetype.png</t>
+          <t>icons-study/07-icones-sources/sysml1/valuetype.png</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/valuetype.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.attributedefinition.svg</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -743,17 +778,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>correspond au type de payload transporte (confirme dans Items.sysml), proche du role de FlowSpecification en v1</t>
+          <t>correspond au type de payload transporte (confirme dans Items.sysml), proche du role de FlowSpecification en v1 - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowspecification.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowspecification.png</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowspecification.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.itemdefinition.svg / icons-study/08-icones-sysml2/sysml.itemusage.svg</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -791,12 +831,17 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowproperty.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowproperty.png</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowproperty.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.itemusagedirectionin.svg</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -833,17 +878,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>confirme dans Ports.sysml - reprendre l'icone port + badge de direction, comme standard.parameter.io.png en UML</t>
+          <t>confirme dans Ports.sysml - reprendre l'icone port + badge de direction, comme standard.parameter.io.png en UML - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowport_in.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowport_in.png</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowport_in.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.portdefinition.svg / icons-study/08-icones-sysml2/sysml.portusagedirectionin.svg</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -880,17 +930,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>idem flowport_in</t>
+          <t>idem flowport_in - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowport_out.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowport_out.png</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowport_out.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.portdefinition.svg / icons-study/08-icones-sysml2/sysml.portusagedirectionout.svg</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -927,17 +982,22 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>idem flowport_in</t>
+          <t>idem flowport_in - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowport_inout.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowport_inout.png</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowport_inout.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.portdefinition.svg / icons-study/08-icones-sysml2/sysml.portusagedirectioninout.svg</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -972,15 +1032,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\port.png</t>
+          <t>icons-study/07-icones-sources/sysml1/port.png</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/port.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.portdefinition.svg / icons-study/08-icones-sysml2/sysml.portusage.svg</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1015,15 +1084,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\interface.png</t>
+          <t>icons-study/07-icones-sources/sysml1/interface.png</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/interface.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.interfacedefinition.svg / icons-study/08-icones-sysml2/sysml.interfaceusage.svg</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1139,17 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\interfacerealization.png</t>
+          <t>icons-study/07-icones-sources/sysml1/interfacerealization.png</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/interfacerealization.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.interfacerealization.svg</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -1103,17 +1186,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>confirme dans Flows.sysml (mot-cle "flow def"/"flow"), pas FlowConnection</t>
+          <t>confirme dans Flows.sysml (mot-cle "flow def"/"flow"), pas FlowConnection - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\itemflow.png</t>
+          <t>icons-study/07-icones-sources/sysml1/itemflow.png</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/itemflow.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.flowdefinition.svg / icons-study/08-icones-sysml2/sysml.flowusage.svg</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1148,15 +1236,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\requirement.png</t>
+          <t>icons-study/07-icones-sources/sysml1/requirement.png</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/requirement.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.requirementdefinition.svg / icons-study/08-icones-sysml2/sysml.requirementusage.svg</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1290,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>confirme dans VerificationCases.sysml</t>
+          <t>confirme dans VerificationCases.sysml - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\testcase.png</t>
+          <t>icons-study/07-icones-sources/sysml1/testcase.png</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/testcase.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.verificationcasedefinition.svg / icons-study/08-icones-sysml2/sysml.verificationcaseusage.svg</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1238,15 +1340,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\viewpoint.png</t>
+          <t>icons-study/07-icones-sources/sysml1/viewpoint.png</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/viewpoint.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.viewpointdefinition.svg / icons-study/08-icones-sysml2/sysml.viewpointusage.svg</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1281,15 +1392,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\view.png</t>
+          <t>icons-study/07-icones-sources/sysml1/view.png</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/view.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.viewdefinition.svg / icons-study/08-icones-sysml2/sysml.viewusage.svg</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1324,15 +1444,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\usecase.png</t>
+          <t>icons-study/07-icones-sources/sysml1/usecase.png</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/usecase.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.usecasedefinition.svg / icons-study/08-icones-sysml2/sysml.usecaseusage.svg</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1369,17 +1498,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>arbre d'etats remplace le concept de machine a etats autonome</t>
+          <t>arbre d'etats remplace le concept de machine a etats autonome - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\statemachine.png</t>
+          <t>icons-study/07-icones-sources/sysml1/statemachine.png</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/statemachine.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.statedefinition.svg / icons-study/08-icones-sysml2/sysml.stateusage.svg</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1414,15 +1548,24 @@
           <t>moyenne</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\activity.png</t>
+          <t>icons-study/07-icones-sources/sysml1/activity.png</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/activity.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.actiondefinition.svg / icons-study/08-icones-sysml2/sysml.actionusage.svg</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1603,17 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\interaction.png</t>
+          <t>icons-study/07-icones-sources/sysml1/interaction.png</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/interaction.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.occurrenceusage.svg</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -1502,17 +1650,22 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>a valider - pas retrouve comme metaclasse dediee, probablement un ItemDefinition specialise</t>
+          <t>a valider - pas retrouve comme metaclasse dediee, probablement un ItemDefinition specialise - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\signal.png</t>
+          <t>icons-study/07-icones-sources/sysml1/signal.png</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/signal.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.itemdefinition.svg / icons-study/08-icones-sysml2/sysml.itemusage.svg</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1702,22 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>confirme dans Allocations.sysml</t>
+          <t>confirme dans Allocations.sysml - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\allocate.png</t>
+          <t>icons-study/07-icones-sources/sysml1/allocate.png</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/allocate.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.allocationdefinition.svg / icons-study/08-icones-sysml2/sysml.allocationusage.svg</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1755,17 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\refine.png</t>
+          <t>icons-study/07-icones-sources/sysml1/refine.png</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/refine.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.refine.svg</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -1633,15 +1796,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\trace.png</t>
+          <t>icons-study/07-icones-sources/sysml1/trace.png</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/trace.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.trace.svg</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1847,13 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\rationale.png</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/rationale.png</t>
+          <t>icons-study/07-icones-sources/sysml1/rationale.png</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -1717,17 +1890,22 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>concept normatif v2 = Concern (confirme dans Requirements.sysml), reprendre problem.png comme base et recolorer</t>
+          <t>concept normatif v2 = Concern (confirme dans Requirements.sysml), reprendre problem.png comme base et recolorer - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\problem.png</t>
+          <t>icons-study/07-icones-sources/sysml1/problem.png</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/problem.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.concerndefinition.svg / icons-study/08-icones-sysml2/sysml.concernusage.svg</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1939,17 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\conform.png</t>
+          <t>icons-study/07-icones-sources/sysml1/conform.png</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/conform.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.conform.svg</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -1799,17 +1982,22 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>notation largement inchangee</t>
+          <t>notation largement inchangee - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\association.png</t>
+          <t>icons-study/07-icones-sources/sysml1/association.png</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/association.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.association.svg</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1840,15 +2028,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\aggregation.png</t>
+          <t>icons-study/07-icones-sources/sysml1/aggregation.png</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/aggregation.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.featuremembershipcompositefalse.svg</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1879,15 +2076,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\composition.png</t>
+          <t>icons-study/07-icones-sources/sysml1/composition.png</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/composition.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.featuremembershipcompositetrue.svg</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1918,15 +2124,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\generalization.png</t>
+          <t>icons-study/07-icones-sources/sysml1/generalization.png</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/generalization.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.specialization.svg</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1957,15 +2172,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\dependency.png</t>
+          <t>icons-study/07-icones-sources/sysml1/dependency.png</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/dependency.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.dependency.svg</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -1998,17 +2222,22 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>pas de dualite Definition/Usage pour un espace de noms</t>
+          <t>pas de dualite Definition/Usage pour un espace de noms - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\package.png</t>
+          <t>icons-study/07-icones-sources/sysml1/package.png</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/package.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.package.svg</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2039,15 +2268,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\packageimport.png</t>
+          <t>icons-study/07-icones-sources/sysml1/packageimport.png</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/packageimport.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.import.svg</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2319,13 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\packagemerge.png</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/packagemerge.png</t>
+          <t>icons-study/07-icones-sources/sysml1/packagemerge.png</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2117,15 +2356,24 @@
           <t>haute</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\elementimport.png</t>
+          <t>icons-study/07-icones-sources/sysml1/elementimport.png</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/elementimport.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.import.svg</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2158,17 +2406,22 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>correction : anciennement place par erreur dans la colonne usage</t>
+          <t>correction : anciennement place par erreur dans la colonne usage - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\enumeration.png</t>
+          <t>icons-study/07-icones-sources/sysml1/enumeration.png</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/enumeration.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.enumerationdefinition.svg</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2454,22 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Definition couverte par la ligne enumeration</t>
+          <t>Definition couverte par la ligne enumeration - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\enumerationliteral.png</t>
+          <t>icons-study/07-icones-sources/sysml1/enumerationliteral.png</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/enumerationliteral.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.enumerationusage.svg</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2503,13 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\datatype.png</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/datatype.png</t>
+          <t>icons-study/07-icones-sources/sysml1/datatype.png</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2543,13 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\class.png</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/class.png</t>
+          <t>icons-study/07-icones-sources/sysml1/class.png</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2587,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\component.png</t>
+          <t>icons-study/07-icones-sources/sysml1/component.png</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/component.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.partdefinitionstereotype.svg</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2369,17 +2634,22 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>confirme dans Connections.sysml</t>
+          <t>confirme dans Connections.sysml - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\connector.png</t>
+          <t>icons-study/07-icones-sources/sysml1/connector.png</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/connector.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.connectiondefinition.svg / icons-study/08-icones-sysml2/sysml.connectionusage.svg</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2412,17 +2682,22 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>pas de sous-type binding explicite trouve dans Connections.sysml - a verifier dans le noyau KerML (Bindings) - icone d'arbre de modele (visuel : simple fleche double, sans les losanges de binding.png qui est l'icone de palette/outil du meme concept, verifie visuellement le 2026-09-24)</t>
+          <t>pas de sous-type binding explicite trouve dans Connections.sysml - a verifier dans le noyau KerML (Bindings) - icone d'arbre de modele (visuel : simple fleche double, sans les losanges de binding.png qui est l'icone de palette/outil du meme concept, verifie visuellement le 2026-09-24) - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\bindingconnector.png</t>
+          <t>icons-study/07-icones-sources/sysml1/bindingconnector.png</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/bindingconnector.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.bindingconnector.svg</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2731,17 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\naryassociation.png</t>
+          <t>icons-study/07-icones-sources/sysml1/naryassociation.png</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/naryassociation.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.relationnaire.svg</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2775,13 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\narylink.png</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/narylink.png</t>
+          <t>icons-study/07-icones-sources/sysml1/narylink.png</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2815,13 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\parameter.png</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/parameter.png</t>
+          <t>icons-study/07-icones-sources/sysml1/parameter.png</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2851,13 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\parameterreturn.png</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/parameterreturn.png</t>
+          <t>icons-study/07-icones-sources/sysml1/parameterreturn.png</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2890,22 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Comment n'a pas de pendant Definition</t>
+          <t>Comment n'a pas de pendant Definition - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\note.png</t>
+          <t>icons-study/07-icones-sources/sysml1/note.png</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/note.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.comment.svg</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2939,13 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\operation.png</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/operation.png</t>
+          <t>icons-study/07-icones-sources/sysml1/operation.png</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2689,17 +2978,22 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>liaison de valeur, pas de dualite Definition/Usage</t>
+          <t>liaison de valeur, pas de dualite Definition/Usage - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\attributelink.png</t>
+          <t>icons-study/07-icones-sources/sysml1/attributelink.png</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/attributelink.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.featurevalue.svg</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -2733,12 +3027,13 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\bindableinstance.png</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/bindableinstance.png</t>
+          <t>icons-study/07-icones-sources/sysml1/bindableinstance.png</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2772,12 +3067,13 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\collaboration.png</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/collaboration.png</t>
+          <t>icons-study/07-icones-sources/sysml1/collaboration.png</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2811,12 +3107,13 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\collaborationuse.png</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/collaborationuse.png</t>
+          <t>icons-study/07-icones-sources/sysml1/collaborationuse.png</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2850,12 +3147,13 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\smartimport.png</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/smartimport.png</t>
+          <t>icons-study/07-icones-sources/sysml1/smartimport.png</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2889,12 +3187,13 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\smartgeneralization.png</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/smartgeneralization.png</t>
+          <t>icons-study/07-icones-sources/sysml1/smartgeneralization.png</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2928,12 +3227,13 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\propertyspecifictype.png</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/propertyspecifictype.png</t>
+          <t>icons-study/07-icones-sources/sysml1/propertyspecifictype.png</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -2967,12 +3267,13 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\participantproperty.png</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/participantproperty.png</t>
+          <t>icons-study/07-icones-sources/sysml1/participantproperty.png</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3307,13 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\distributedproperty.png</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/distributedproperty.png</t>
+          <t>icons-study/07-icones-sources/sysml1/distributedproperty.png</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3045,12 +3347,13 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\connectorproperty.png</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/connectorproperty.png</t>
+          <t>icons-study/07-icones-sources/sysml1/connectorproperty.png</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3084,12 +3387,13 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\optional.png</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/optional.png</t>
+          <t>icons-study/07-icones-sources/sysml1/optional.png</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3427,13 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\continuous.png</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/continuous.png</t>
+          <t>icons-study/07-icones-sources/sysml1/continuous.png</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3467,13 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\discrete.png</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/discrete.png</t>
+          <t>icons-study/07-icones-sources/sysml1/discrete.png</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3201,12 +3507,13 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\continuousparameter.png</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/continuousparameter.png</t>
+          <t>icons-study/07-icones-sources/sysml1/continuousparameter.png</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3547,13 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\discreteparameter.png</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/discreteparameter.png</t>
+          <t>icons-study/07-icones-sources/sysml1/discreteparameter.png</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3587,13 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\rate.png</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/rate.png</t>
+          <t>icons-study/07-icones-sources/sysml1/rate.png</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3318,12 +3627,13 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\rateparameter.png</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/rateparameter.png</t>
+          <t>icons-study/07-icones-sources/sysml1/rateparameter.png</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3667,13 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\probability.png</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/probability.png</t>
+          <t>icons-study/07-icones-sources/sysml1/probability.png</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3707,13 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\unit.png</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/unit.png</t>
+          <t>icons-study/07-icones-sources/sysml1/unit.png</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3435,12 +3747,13 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\quantitykind.png</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/quantitykind.png</t>
+          <t>icons-study/07-icones-sources/sysml1/quantitykind.png</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3473,17 +3786,22 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Definition couverte par la ligne interface</t>
+          <t>Definition couverte par la ligne interface - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\providedinterface.png</t>
+          <t>icons-study/07-icones-sources/sysml1/providedinterface.png</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/providedinterface.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.interfaceusageportprovided.svg</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -3516,17 +3834,22 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Definition couverte par la ligne interface</t>
+          <t>Definition couverte par la ligne interface - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\requiredinterface.png</t>
+          <t>icons-study/07-icones-sources/sysml1/requiredinterface.png</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/requiredinterface.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.interfaceusageportrequired.svg</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3883,13 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\umlcomposition.png</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/umlcomposition.png</t>
+          <t>icons-study/07-icones-sources/sysml1/umlcomposition.png</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3923,13 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\associationclass.png</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/associationclass.png</t>
+          <t>icons-study/07-icones-sources/sysml1/associationclass.png</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3641,17 +3966,22 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>meme correction que itemflow, confirme dans Flows.sysml</t>
+          <t>meme correction que itemflow, confirme dans Flows.sysml - PRODUIT (2026-09-24) : icones bleu validees par le PO, fichiers finaux en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\informationflow.png</t>
+          <t>icons-study/07-icones-sources/sysml1/informationflow.png</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/informationflow.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.flowdefinition.svg / icons-study/08-icones-sysml2/sysml.flowusage.svg</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -3685,12 +4015,13 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\templatebinding.png</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/templatebinding.png</t>
+          <t>icons-study/07-icones-sources/sysml1/templatebinding.png</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3724,12 +4055,13 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\raisedexception.png</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/raisedexception.png</t>
+          <t>icons-study/07-icones-sources/sysml1/raisedexception.png</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3762,17 +4094,22 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>reference n'a pas de pendant Definition en KerML (mot-cle de non-appartenance)</t>
+          <t>reference n'a pas de pendant Definition en KerML (mot-cle de non-appartenance) - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\reference.png</t>
+          <t>icons-study/07-icones-sources/sysml1/reference.png</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/reference.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.referenceusage.svg</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -3806,12 +4143,13 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysml.png</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysml.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysml.png</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3845,12 +4183,13 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\blockdiagram.png</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/blockdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/blockdiagram.png</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3884,12 +4223,13 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\internalblockdiagram.png</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/internalblockdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/internalblockdiagram.png</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3919,12 +4259,13 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\packagediagram.png</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/packagediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/packagediagram.png</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3954,12 +4295,13 @@
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\parametricdiagram.png</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/parametricdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/parametricdiagram.png</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -3989,12 +4331,13 @@
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysmlactivitydiagram.png</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysmlactivitydiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysmlactivitydiagram.png</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4024,12 +4367,13 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysmlrequirementdiagram.png</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysmlrequirementdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysmlrequirementdiagram.png</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4403,13 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysmlsequencediagram.png</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysmlsequencediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysmlsequencediagram.png</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4439,13 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysmlstatemachinediagram.png</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysmlstatemachinediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysmlstatemachinediagram.png</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4475,13 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysmlusecasediagram.png</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysmlusecasediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysmlusecasediagram.png</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4515,13 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewactivitydiagram.png</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewactivitydiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewactivitydiagram.png</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4555,13 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewblockdiagram.png</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewblockdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewblockdiagram.png</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4246,12 +4595,13 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewinternalblockdiagram.png</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewinternalblockdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewinternalblockdiagram.png</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4635,13 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewpackagediagram.png</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewpackagediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewpackagediagram.png</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4324,12 +4675,13 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewparametricdiagram.png</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewparametricdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewparametricdiagram.png</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4715,13 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewsequencediagram.png</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewsequencediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewsequencediagram.png</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4755,13 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewstatediagram.png</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewstatediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewstatediagram.png</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4795,13 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\previewusecasediagram.png</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/previewusecasediagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/previewusecasediagram.png</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4838,16 @@
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.metadatadefinition.svg / icons-study/08-icones-sysml2/sysml.metadatausage.svg</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr"/>
@@ -4518,7 +4882,16 @@
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.analysiscasedefinition.svg / icons-study/08-icones-sysml2/sysml.analysiscaseusage.svg</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr"/>
@@ -4554,12 +4927,17 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.artifact.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.artifact.png</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.artifact.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.renderingdefinitiontextual.svg / icons-study/08-icones-sysml2/sysml.renderingusage.svg</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4597,12 +4975,17 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.event.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.event.png</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.event.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.occurrencedefinition.svg / icons-study/08-icones-sysml2/sysml.occurrenceusage.svg</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4640,12 +5023,17 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.instance.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.instance.png</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.instance.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.individualdefinition.svg / icons-study/08-icones-sysml2/sysml.individualusage.svg</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4678,17 +5066,22 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>variante grande taille (48px) de block.png, meme concept</t>
+          <t>variante grande taille (48px) de block.png, meme concept - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\block48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/block48.png</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/block48.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.partdefinition.svg</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -4721,17 +5114,22 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>variante 48px de constraintblock.png</t>
+          <t>variante 48px de constraintblock.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\constraintblock48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/constraintblock48.png</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/constraintblock48.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.constraintdefinition.svg</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -4764,17 +5162,22 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>variante 48px de valuetype.png</t>
+          <t>variante 48px de valuetype.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\valuetype48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/valuetype48.png</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/valuetype48.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.attributedefinition.svg</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -4811,17 +5214,22 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>variante 48px de view.png</t>
+          <t>variante 48px de view.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\view48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/view48.png</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/view48.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.viewdefinition.svg / icons-study/08-icones-sysml2/sysml.viewusage.svg</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -4858,17 +5266,22 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>variante 48px de viewpoint.png</t>
+          <t>variante 48px de viewpoint.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\viewpoint48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/viewpoint48.png</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/viewpoint48.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.viewpointdefinition.svg / icons-study/08-icones-sysml2/sysml.viewpointusage.svg</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -4902,12 +5315,13 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\unit48.png</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/unit48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/unit48.png</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4941,12 +5355,13 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\quantitykind48.png</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/quantitykind48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/quantitykind48.png</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -4983,17 +5398,22 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>variante 48px de flowspecification.png</t>
+          <t>variante 48px de flowspecification.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowspecification48.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowspecification48.png</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowspecification48.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.itemdefinition.svg / icons-study/08-icones-sysml2/sysml.itemusage.svg</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5026,17 +5446,22 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>icone de palette/outil de diagramme pour tracer un binding connector (visuel : deux losanges relies par une double fleche) - a distinguer de bindingconnector.png qui semble etre l'icone d'arbre de modele du meme concept (verifie visuellement le 2026-09-24)</t>
+          <t>icone de palette/outil de diagramme pour tracer un binding connector (visuel : deux losanges relies par une double fleche) - a distinguer de bindingconnector.png qui semble etre l'icone d'arbre de modele du meme concept (verifie visuellement le 2026-09-24) - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\binding.png</t>
+          <t>icons-study/07-icones-sources/sysml1/binding.png</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/binding.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.bindingconnector.svg</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5495,13 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\link_delegate.png</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/link_delegate.png</t>
+          <t>icons-study/07-icones-sources/sysml1/link_delegate.png</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5109,12 +5535,13 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysmlback.png</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysmlback.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysmlback.png</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5148,12 +5575,13 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\backback.png</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/backback.png</t>
+          <t>icons-study/07-icones-sources/sysml1/backback.png</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5191,12 +5619,17 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\usage.png</t>
+          <t>icons-study/07-icones-sources/sysml1/usage.png</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/usage.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.usage.svg</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5225,17 +5658,22 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>pas de base SysML1 - repli UML : standard.acceptsignalaction.png - Definition couverte par ActionDefinition (ligne activity), ce sous-type n'a pas de Definition dediee</t>
+          <t>pas de base SysML1 - repli UML : standard.acceptsignalaction.png - Definition couverte par ActionDefinition (ligne activity), ce sous-type n'a pas de Definition dediee - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.acceptsignalaction.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.acceptsignalaction.png</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.acceptsignalaction.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.acceptactionusage.svg</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5264,17 +5702,22 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>pas de base SysML1 - repli UML : standard.sendsignalaction.png - idem AcceptActionUsage</t>
+          <t>pas de base SysML1 - repli UML : standard.sendsignalaction.png - idem AcceptActionUsage - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.sendsignalaction.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.sendsignalaction.png</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.sendsignalaction.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.sendactionusage.svg</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5750,16 @@
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.assignmentactionusage.svg</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr"/>
@@ -5339,12 +5791,17 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.conditionalnode.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.conditionalnode.png</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.conditionalnode.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.ifactionusage.svg</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5835,17 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.loopnode.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.loopnode.png</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.loopnode.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.loopactionusage.svg</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5879,17 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.callbehavioraction.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.callbehavioraction.png</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.callbehavioraction.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.performactionusage.svg</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5923,17 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.flowfinalnode.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.flowfinalnode.png</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.flowfinalnode.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.terminateactionusage.svg</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5967,17 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.forkjoinnode.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.forkjoinnode.png</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.forkjoinnode.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.forknode.svg</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5534,12 +6011,17 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.forkjoinnode.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.forkjoinnode.png</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.forkjoinnode.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.joinnode.svg</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5568,17 +6050,22 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>pas de base SysML1 - repli UML : standard.mergenode.png</t>
+          <t>pas de base SysML1 - repli UML : standard.mergenode.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.mergenode.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.mergenode.png</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.mergenode.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.mergenode.svg</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5607,17 +6094,22 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>pas de base SysML1 - repli UML : standard.decisionmergenode.png</t>
+          <t>pas de base SysML1 - repli UML : standard.decisionmergenode.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.decisionmergenode.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.decisionmergenode.png</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.decisionmergenode.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.decisionnode.svg</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5646,17 +6138,22 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>pas de base SysML1 - repli UML : standard.transition.png - Definition non applicable (relation de StateUsage)</t>
+          <t>pas de base SysML1 - repli UML : standard.transition.png - Definition non applicable (relation de StateUsage) - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.transition.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.transition.png</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.transition.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.transitionusage.svg</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5690,12 +6187,17 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.event.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.event.png</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.event.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.eventoccurrenceusage.svg</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5729,12 +6231,17 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.state.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.state.png</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.state.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.exhibitstateusage.svg</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -5763,11 +6270,20 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>variante de ConstraintUsage (assertion) - badge sur la base constraintproperty.png</t>
+          <t>variante de ConstraintUsage (assertion) - badge sur la base constraintproperty.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.assertconstraintusage.svg</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr"/>
@@ -5794,11 +6310,20 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>variante permanente de ConstraintUsage - badge sur la base constraintproperty.png</t>
+          <t>variante permanente de ConstraintUsage - badge sur la base constraintproperty.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.invariant.svg</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr"/>
@@ -5825,11 +6350,20 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>variante miroir de PortDefinition (port conjugue) - badge sur la base port.png</t>
+          <t>variante miroir de PortDefinition (port conjugue) - badge sur la base port.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.conjugatedportdefinition.svg</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr"/>
@@ -5860,7 +6394,16 @@
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.bindingconnectorasusage.svg</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr"/>
@@ -5891,7 +6434,16 @@
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.satisfyrequirementusage.svg</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr"/>
@@ -5918,17 +6470,22 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>pas de base SysML1 - repli UML : standard.usecasedependencyinclude.png</t>
+          <t>pas de base SysML1 - repli UML : standard.usecasedependencyinclude.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.usecasedependencyinclude.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.usecasedependencyinclude.png</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.usecasedependencyinclude.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.includeusecaseusage.svg</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -5965,7 +6522,16 @@
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.calculationdefinition.svg / icons-study/08-icones-sysml2/sysml.calculationusage.svg</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr"/>
@@ -5992,11 +6558,20 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>variante de Package (bibliotheque) - badge sur la base package.png</t>
+          <t>variante de Package (bibliotheque) - badge sur la base package.png - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>icons-study/08-icones-sysml2/sysml.librarypackage.svg</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr"/>
@@ -6023,13 +6598,22 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>icone deja existante dans le module cible (sysml.sysmlproject.png) - aucune action requise</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr"/>
+          <t>icone deja existante dans le module cible (sysml.sysmlproject.png) - aucune action requise - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>H:\modelio\work\modelio-source\modelio\sysml\sysml.ui\mmimages\sysml.sysmlproject.png</t>
+        </is>
+      </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
           <t>H:\modelio\work\modelio-source\modelio\sysml\sysml.ui\mmimages\sysml.sysmlproject.png</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -6058,17 +6642,22 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>pas de base SysML1 utilisable - repli UML : standard.attribute.png (lettre 'a' generique, pas de nom de type grave en dur contrairement a valuetype.png) - trou expose par la correction du 2026-09-24 sur la ligne valuetype</t>
+          <t>pas de base SysML1 utilisable - repli UML : standard.attribute.png (lettre 'a' generique, pas de nom de type grave en dur contrairement a valuetype.png) - trou expose par la correction du 2026-09-24 sur la ligne valuetype - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>H:\modelio\work\modelio-source\modelio\uml\uml.ui\mmimages\standard.attribute.png</t>
+          <t>icons-study/07-icones-sources/uml/standard.attribute.png</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>icons-study/04-sources-brutes/uml/standard.attribute.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.attributeusage.svg</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -6110,12 +6699,17 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\actor.png</t>
+          <t>icons-study/07-icones-sources/sysml1/actor.png</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/actor.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.partdefinitionstereotype.svg / icons-study/08-icones-sysml2/sysml.partusagestereotype.svg</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6743,13 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\constraint.png</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/constraint.png</t>
+          <t>icons-study/07-icones-sources/sysml1/constraint.png</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -6191,17 +6786,22 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>vignette de diagramme de flowport_in.png, meme concept</t>
+          <t>vignette de diagramme de flowport_in.png, meme concept - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowport_indiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowport_indiagram.png</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowport_indiagram.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.portdefinition.svg / icons-study/08-icones-sysml2/sysml.portusagedirectionin.svg</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -6238,17 +6838,22 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>vignette de diagramme de flowport_inout.png, meme concept</t>
+          <t>vignette de diagramme de flowport_inout.png, meme concept - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowport_inoutdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowport_inoutdiagram.png</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowport_inoutdiagram.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.portdefinition.svg / icons-study/08-icones-sysml2/sysml.portusagedirectioninout.svg</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -6285,17 +6890,22 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>vignette de diagramme de flowport_out.png, meme concept</t>
+          <t>vignette de diagramme de flowport_out.png, meme concept - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\flowport_outdiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/flowport_outdiagram.png</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/flowport_outdiagram.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.portdefinition.svg / icons-study/08-icones-sysml2/sysml.portusagedirectionout.svg</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6939,13 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\sysmldiagram.png</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>icons-study/07-icones-sources/sysmldiagram.png</t>
+          <t>icons-study/07-icones-sources/sysml1/sysmldiagram.png</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>a_faire</t>
         </is>
       </c>
     </row>
@@ -6367,17 +6978,22 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>doublon visuel confirme de trace.png (image identique, verifie visuellement le 2026-09-24) - ne garder qu'un seul des deux fichiers en base de production, l'autre est superflu</t>
+          <t>doublon visuel confirme de trace.png (image identique, verifie visuellement le 2026-09-24) - ne garder qu'un seul des deux fichiers en base de production, l'autre est superflu - PRODUIT (2026-09-24) : icone bleu validee par le PO, fichier final en place a chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\frekik\Documents\GIT\ExtensionsForModelio\SysMLArchitect\src\main\conf\res\icons\traceability.png</t>
+          <t>icons-study/07-icones-sources/sysml1/traceability.png</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>icons-study/07-icones-sources/traceability.png</t>
+          <t>icons-study/08-icones-sysml2/sysml.trace.svg</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>produit</t>
         </is>
       </c>
     </row>
@@ -6392,7 +7008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6498,57 +7114,69 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>chemin_source</t>
+          <t>chemin_icone_source</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Chemin absolu du fichier source d'origine (SysMLArchitect ou UML mmimages). Vide si aucune base (action=creer sans repli).</t>
+          <t>Chemin, dans ce depot, de l'icone de base a partir de laquelle on travaille : icons-study/07-icones-sources/sysml1/ (icone SysML1) ou icons-study/07-icones-sources/uml/ (repli UML). Vide si action=creer sans aucune base.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>chemin_destination</t>
+          <t>chemin_icone_sysml2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Chemin (relatif au depot ou absolu si hors depot) ou vit la copie de ce fichier : icons-study/07-icones-sources/ pour les icones SysML1 (base de depart complete), icons-study/04-sources-brutes/uml/ pour les replis UML utilises comme base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+          <t>Chemin ou sera creee l'icone SysML v2 finale (SVG) : icons-study/08-icones-sysml2/sysml.&lt;concept-en-minuscules&gt;.svg. Deux chemins separes par ' / ' quand la ligne couvre Definition ET Usage (deux fichiers distincts). Cas particulier SysMLProject : pointe directement vers l'icone deja existante dans le module cible (action=aucune, rien a produire).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>avancement</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>a_faire (rien produit) / a_valider (genere dans 09-icones-a-valider/, en attente de validation PO) / produit (valide, copie dans 08-icones-sysml2/). Calcule automatiquement a partir des fichiers presents sur le disque - ne pas editer a la main, regenerer via le script si l'etat change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Notes generales :</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>- Dualite Definition/Usage : chaque concept SysML v2 existe en deux versions - la Definition (le blueprint reutilisable, ex. "qu'est-ce qu'un moteur") et l'Usage (une occurrence de ce blueprint dans un contexte precis, ex. "le moteur de cette voiture"). SysML v1 n'avait souvent qu'une seule icone la ou v2 en demande deux.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>- Variantes de taille (ex. block48 a cote de block) : meme pictogramme que la ligne de base, juste en plus grande taille (48px vs 24px), utilisee dans les assistants de creation/palettes plutot que l'arbre de modele. Meme concept SysML v2, pas de duplication a produire.</t>
+          <t>- Dualite Definition/Usage : chaque concept SysML v2 existe en deux versions - la Definition (le blueprint reutilisable, ex. "qu'est-ce qu'un moteur") et l'Usage (une occurrence de ce blueprint dans un contexte precis, ex. "le moteur de cette voiture"). SysML v1 n'avait souvent qu'une seule icone la ou v2 en demande deux.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>- Notation officielle SysML v2 (spec, verifiee le 2026-09-24) : aucune icone/pictogramme propose par la norme. Seule distinction graphique normative pour Definition/Usage : coins droits (Definition) vs coins arrondis (Usage) sur le rectangle a compartiments. Le jeu d'icones Modelio reste une amelioration d'ergonomie propre a l'outil.</t>
+          <t>- Variantes de taille (ex. block48 a cote de block) : meme pictogramme que la ligne de base, juste en plus grande taille (48px vs 24px), utilisee dans les assistants de creation/palettes plutot que l'arbre de modele. Meme concept SysML v2, pas de duplication a produire.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>- Notation officielle SysML v2 (spec, verifiee le 2026-09-24) : aucune icone/pictogramme propose par la norme. Seule distinction graphique normative pour Definition/Usage : coins droits (Definition) vs coins arrondis (Usage) sur le rectangle a compartiments. Le jeu d'icones Modelio reste une amelioration d'ergonomie propre a l'outil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>- Base de depart (2026-09-24, validee PO) : les 117 icones SysMLArchitect ont ete copiees dans ce depot sous icons-study/07-icones-sources/ (copie, pas de suppression des originaux dans le depot ExtensionsForModelio). Couleur retenue : bleu (#2c70ba), style Definition/Usage (soulignement) valide sur les 3 icones prototype (block, port, requirement) - une deuxieme teinte (option violet) reste possible en complement si besoin plus tard.</t>
         </is>
@@ -6560,7 +7188,7 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
